--- a/artfynd/A 29675-2024 artfynd.xlsx
+++ b/artfynd/A 29675-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121127723</v>
       </c>
       <c r="B2" t="n">
-        <v>79546</v>
+        <v>79549</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 29675-2024 artfynd.xlsx
+++ b/artfynd/A 29675-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121127723</v>
       </c>
       <c r="B2" t="n">
-        <v>79549</v>
+        <v>79552</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 29675-2024 artfynd.xlsx
+++ b/artfynd/A 29675-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121127723</v>
       </c>
       <c r="B2" t="n">
-        <v>79552</v>
+        <v>79555</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 29675-2024 artfynd.xlsx
+++ b/artfynd/A 29675-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -789,6 +789,2979 @@
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>121589879</v>
+      </c>
+      <c r="B3" t="n">
+        <v>79718</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>6461</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Norrlandslav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Nephroma arcticum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Jokkmokksmyran, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>726622</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7355532</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>121589877</v>
+      </c>
+      <c r="B4" t="n">
+        <v>78609</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Jokkmokksmyran, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>726675</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7355240</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>121589890</v>
+      </c>
+      <c r="B5" t="n">
+        <v>78609</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Jokkmokksmyran, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>726689</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7355064</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>121589902</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79594</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Jokkmokksmyran, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>726867</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7354803</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>121589878</v>
+      </c>
+      <c r="B7" t="n">
+        <v>82393</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Jokkmokksmyran, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>726646</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7355247</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>121589899</v>
+      </c>
+      <c r="B8" t="n">
+        <v>82393</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Jokkmokksmyran, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>726760</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7354944</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>121589893</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79719</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Jokkmokksmyran, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>726716</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7354943</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>121589872</v>
+      </c>
+      <c r="B10" t="n">
+        <v>56568</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Jokkmokksmyran, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>726920</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7355536</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>121589900</v>
+      </c>
+      <c r="B11" t="n">
+        <v>78691</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>864</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knottrig blåslav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Hypogymnia bitteri</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Lynge) Ahti</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Jokkmokksmyran, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>726863</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7354860</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>121589876</v>
+      </c>
+      <c r="B12" t="n">
+        <v>82393</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Jokkmokksmyran, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>726693</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7355235</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>121589871</v>
+      </c>
+      <c r="B13" t="n">
+        <v>97059</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Jokkmokksmyran, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>726939</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7355544</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>121589881</v>
+      </c>
+      <c r="B14" t="n">
+        <v>97065</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Jokkmokksmyran, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>726603</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7355549</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>121589884</v>
+      </c>
+      <c r="B15" t="n">
+        <v>78609</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Jokkmokksmyran, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>726405</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7355166</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>121589892</v>
+      </c>
+      <c r="B16" t="n">
+        <v>78609</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Jokkmokksmyran, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>726717</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7354967</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>121589895</v>
+      </c>
+      <c r="B17" t="n">
+        <v>97059</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Jokkmokksmyran, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>726866</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7354811</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>121589875</v>
+      </c>
+      <c r="B18" t="n">
+        <v>79719</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Jokkmokksmyran, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>726667</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7355228</v>
+      </c>
+      <c r="S18" t="n">
+        <v>25</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>121589891</v>
+      </c>
+      <c r="B19" t="n">
+        <v>79726</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Jokkmokksmyran, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>726725</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7354940</v>
+      </c>
+      <c r="S19" t="n">
+        <v>25</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>121589873</v>
+      </c>
+      <c r="B20" t="n">
+        <v>79719</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Jokkmokksmyran, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>726754</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7355172</v>
+      </c>
+      <c r="S20" t="n">
+        <v>25</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>121589874</v>
+      </c>
+      <c r="B21" t="n">
+        <v>78609</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Jokkmokksmyran, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>726754</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7355194</v>
+      </c>
+      <c r="S21" t="n">
+        <v>25</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>121589883</v>
+      </c>
+      <c r="B22" t="n">
+        <v>78691</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>864</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Knottrig blåslav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Hypogymnia bitteri</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Lynge) Ahti</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Jokkmokksmyran, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>726404</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7355159</v>
+      </c>
+      <c r="S22" t="n">
+        <v>25</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>121589882</v>
+      </c>
+      <c r="B23" t="n">
+        <v>78609</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Jokkmokksmyran, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>726600</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7355553</v>
+      </c>
+      <c r="S23" t="n">
+        <v>25</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>121589880</v>
+      </c>
+      <c r="B24" t="n">
+        <v>91674</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>4787</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Granriska</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Lactarius zonarioides</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Kühner &amp; Romagn.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Jokkmokksmyran, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>726609</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7355531</v>
+      </c>
+      <c r="S24" t="n">
+        <v>25</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>121589897</v>
+      </c>
+      <c r="B25" t="n">
+        <v>79718</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6461</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Norrlandslav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Nephroma arcticum</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Jokkmokksmyran, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>726759</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7354946</v>
+      </c>
+      <c r="S25" t="n">
+        <v>25</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>121589898</v>
+      </c>
+      <c r="B26" t="n">
+        <v>91674</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>4787</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Granriska</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Lactarius zonarioides</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Kühner &amp; Romagn.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Jokkmokksmyran, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>726741</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7354942</v>
+      </c>
+      <c r="S26" t="n">
+        <v>25</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>121589901</v>
+      </c>
+      <c r="B27" t="n">
+        <v>90738</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Jokkmokksmyran, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>726863</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7354872</v>
+      </c>
+      <c r="S27" t="n">
+        <v>25</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>121589894</v>
+      </c>
+      <c r="B28" t="n">
+        <v>79691</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Jokkmokksmyran, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>726724</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7354941</v>
+      </c>
+      <c r="S28" t="n">
+        <v>25</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>121589896</v>
+      </c>
+      <c r="B29" t="n">
+        <v>78609</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Jokkmokksmyran, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>726865</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7354873</v>
+      </c>
+      <c r="S29" t="n">
+        <v>25</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 29675-2024 artfynd.xlsx
+++ b/artfynd/A 29675-2024 artfynd.xlsx
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121589879</v>
+        <v>121589896</v>
       </c>
       <c r="B3" t="n">
-        <v>79718</v>
+        <v>78609</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,25 +803,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -838,10 +838,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>726622</v>
+        <v>726865</v>
       </c>
       <c r="R3" t="n">
-        <v>7355532</v>
+        <v>7354873</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -901,7 +901,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121589877</v>
+        <v>121589882</v>
       </c>
       <c r="B4" t="n">
         <v>78609</v>
@@ -948,10 +948,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>726675</v>
+        <v>726600</v>
       </c>
       <c r="R4" t="n">
-        <v>7355240</v>
+        <v>7355553</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121589890</v>
+        <v>121589871</v>
       </c>
       <c r="B5" t="n">
-        <v>78609</v>
+        <v>97059</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,25 +1023,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1051,6 +1051,7 @@
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1058,10 +1059,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>726689</v>
+        <v>726939</v>
       </c>
       <c r="R5" t="n">
-        <v>7355064</v>
+        <v>7355544</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1121,10 +1122,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121589902</v>
+        <v>121589901</v>
       </c>
       <c r="B6" t="n">
-        <v>79594</v>
+        <v>90738</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1133,25 +1134,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6456</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1168,10 +1169,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>726867</v>
+        <v>726863</v>
       </c>
       <c r="R6" t="n">
-        <v>7354803</v>
+        <v>7354872</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1231,10 +1232,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121589878</v>
+        <v>121589890</v>
       </c>
       <c r="B7" t="n">
-        <v>82393</v>
+        <v>78609</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1247,21 +1248,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1278,10 +1279,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>726646</v>
+        <v>726689</v>
       </c>
       <c r="R7" t="n">
-        <v>7355247</v>
+        <v>7355064</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1341,10 +1342,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121589899</v>
+        <v>121589891</v>
       </c>
       <c r="B8" t="n">
-        <v>82393</v>
+        <v>79726</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1353,25 +1354,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1312</v>
+        <v>6464</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1388,10 +1389,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>726760</v>
+        <v>726725</v>
       </c>
       <c r="R8" t="n">
-        <v>7354944</v>
+        <v>7354940</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1418,12 +1419,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1451,10 +1452,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121589893</v>
+        <v>121589876</v>
       </c>
       <c r="B9" t="n">
-        <v>79719</v>
+        <v>82393</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1463,25 +1464,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6462</v>
+        <v>1312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1498,10 +1499,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>726716</v>
+        <v>726693</v>
       </c>
       <c r="R9" t="n">
-        <v>7354943</v>
+        <v>7355235</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1528,12 +1529,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1561,10 +1562,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121589872</v>
+        <v>121589899</v>
       </c>
       <c r="B10" t="n">
-        <v>56568</v>
+        <v>82393</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1573,25 +1574,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>1312</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1599,9 +1600,8 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1609,10 +1609,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>726920</v>
+        <v>726760</v>
       </c>
       <c r="R10" t="n">
-        <v>7355536</v>
+        <v>7354944</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1639,12 +1639,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1653,6 +1653,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1671,10 +1672,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121589900</v>
+        <v>121589877</v>
       </c>
       <c r="B11" t="n">
-        <v>78691</v>
+        <v>78609</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1687,21 +1688,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1718,10 +1719,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>726863</v>
+        <v>726675</v>
       </c>
       <c r="R11" t="n">
-        <v>7354860</v>
+        <v>7355240</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1748,12 +1749,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1781,10 +1782,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121589876</v>
+        <v>121589884</v>
       </c>
       <c r="B12" t="n">
-        <v>82393</v>
+        <v>78609</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1797,21 +1798,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1828,10 +1829,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>726693</v>
+        <v>726405</v>
       </c>
       <c r="R12" t="n">
-        <v>7355235</v>
+        <v>7355166</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1891,10 +1892,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121589871</v>
+        <v>121589880</v>
       </c>
       <c r="B13" t="n">
-        <v>97059</v>
+        <v>91674</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1907,21 +1908,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221945</v>
+        <v>4787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Granriska</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lactarius zonarioides</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Kühner &amp; Romagn.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1931,7 +1932,6 @@
       </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>726939</v>
+        <v>726609</v>
       </c>
       <c r="R13" t="n">
-        <v>7355544</v>
+        <v>7355531</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2002,10 +2002,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121589881</v>
+        <v>121589875</v>
       </c>
       <c r="B14" t="n">
-        <v>97065</v>
+        <v>79719</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2018,21 +2018,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221941</v>
+        <v>6462</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2042,7 +2042,6 @@
       </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2050,10 +2049,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>726603</v>
+        <v>726667</v>
       </c>
       <c r="R14" t="n">
-        <v>7355549</v>
+        <v>7355228</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2113,10 +2112,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121589884</v>
+        <v>121589894</v>
       </c>
       <c r="B15" t="n">
-        <v>78609</v>
+        <v>79691</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2129,21 +2128,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2160,10 +2159,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>726405</v>
+        <v>726724</v>
       </c>
       <c r="R15" t="n">
-        <v>7355166</v>
+        <v>7354941</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2223,10 +2222,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121589892</v>
+        <v>121589872</v>
       </c>
       <c r="B16" t="n">
-        <v>78609</v>
+        <v>56568</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2235,25 +2234,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2261,8 +2260,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2270,10 +2270,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>726717</v>
+        <v>726920</v>
       </c>
       <c r="R16" t="n">
-        <v>7354967</v>
+        <v>7355536</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2314,7 +2314,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2333,10 +2332,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121589895</v>
+        <v>121589874</v>
       </c>
       <c r="B17" t="n">
-        <v>97059</v>
+        <v>78609</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2345,25 +2344,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2373,7 +2372,6 @@
       </c>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2381,10 +2379,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>726866</v>
+        <v>726754</v>
       </c>
       <c r="R17" t="n">
-        <v>7354811</v>
+        <v>7355194</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2444,10 +2442,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121589875</v>
+        <v>121589879</v>
       </c>
       <c r="B18" t="n">
-        <v>79719</v>
+        <v>79718</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2460,21 +2458,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6462</v>
+        <v>6461</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2491,10 +2489,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>726667</v>
+        <v>726622</v>
       </c>
       <c r="R18" t="n">
-        <v>7355228</v>
+        <v>7355532</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2554,10 +2552,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121589891</v>
+        <v>121589895</v>
       </c>
       <c r="B19" t="n">
-        <v>79726</v>
+        <v>97059</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2570,21 +2568,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6464</v>
+        <v>221945</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2594,6 +2592,7 @@
       </c>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2601,10 +2600,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>726725</v>
+        <v>726866</v>
       </c>
       <c r="R19" t="n">
-        <v>7354940</v>
+        <v>7354811</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2664,10 +2663,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121589873</v>
+        <v>121589883</v>
       </c>
       <c r="B20" t="n">
-        <v>79719</v>
+        <v>78691</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2676,25 +2675,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6462</v>
+        <v>864</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2711,10 +2710,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>726754</v>
+        <v>726404</v>
       </c>
       <c r="R20" t="n">
-        <v>7355172</v>
+        <v>7355159</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2774,10 +2773,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121589874</v>
+        <v>121589881</v>
       </c>
       <c r="B21" t="n">
-        <v>78609</v>
+        <v>97065</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2786,25 +2785,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2814,6 +2813,7 @@
       </c>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2821,10 +2821,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>726754</v>
+        <v>726603</v>
       </c>
       <c r="R21" t="n">
-        <v>7355194</v>
+        <v>7355549</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2884,10 +2884,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121589883</v>
+        <v>121589898</v>
       </c>
       <c r="B22" t="n">
-        <v>78691</v>
+        <v>91674</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2896,25 +2896,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>864</v>
+        <v>4787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Granriska</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lactarius zonarioides</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>Kühner &amp; Romagn.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2931,10 +2931,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>726404</v>
+        <v>726741</v>
       </c>
       <c r="R22" t="n">
-        <v>7355159</v>
+        <v>7354942</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2994,10 +2994,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121589882</v>
+        <v>121589897</v>
       </c>
       <c r="B23" t="n">
-        <v>78609</v>
+        <v>79718</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3006,25 +3006,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -3041,10 +3041,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>726600</v>
+        <v>726759</v>
       </c>
       <c r="R23" t="n">
-        <v>7355553</v>
+        <v>7354946</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3104,10 +3104,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121589880</v>
+        <v>121589893</v>
       </c>
       <c r="B24" t="n">
-        <v>91674</v>
+        <v>79719</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3120,21 +3120,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4787</v>
+        <v>6462</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granriska</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lactarius zonarioides</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Kühner &amp; Romagn.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3151,10 +3151,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>726609</v>
+        <v>726716</v>
       </c>
       <c r="R24" t="n">
-        <v>7355531</v>
+        <v>7354943</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3181,12 +3181,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3214,10 +3214,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121589897</v>
+        <v>121589892</v>
       </c>
       <c r="B25" t="n">
-        <v>79718</v>
+        <v>78609</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3226,25 +3226,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3261,10 +3261,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>726759</v>
+        <v>726717</v>
       </c>
       <c r="R25" t="n">
-        <v>7354946</v>
+        <v>7354967</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3324,10 +3324,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121589898</v>
+        <v>121589873</v>
       </c>
       <c r="B26" t="n">
-        <v>91674</v>
+        <v>79719</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3340,21 +3340,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4787</v>
+        <v>6462</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granriska</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lactarius zonarioides</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Kühner &amp; Romagn.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3371,10 +3371,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>726741</v>
+        <v>726754</v>
       </c>
       <c r="R26" t="n">
-        <v>7354942</v>
+        <v>7355172</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3434,10 +3434,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121589901</v>
+        <v>121589900</v>
       </c>
       <c r="B27" t="n">
-        <v>90738</v>
+        <v>78691</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3450,21 +3450,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5432</v>
+        <v>864</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3484,7 +3484,7 @@
         <v>726863</v>
       </c>
       <c r="R27" t="n">
-        <v>7354872</v>
+        <v>7354860</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3511,12 +3511,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3544,10 +3544,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121589894</v>
+        <v>121589902</v>
       </c>
       <c r="B28" t="n">
-        <v>79691</v>
+        <v>79594</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3556,25 +3556,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2081</v>
+        <v>6456</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3591,10 +3591,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>726724</v>
+        <v>726867</v>
       </c>
       <c r="R28" t="n">
-        <v>7354941</v>
+        <v>7354803</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3654,10 +3654,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121589896</v>
+        <v>121589878</v>
       </c>
       <c r="B29" t="n">
-        <v>78609</v>
+        <v>82393</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3670,21 +3670,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3701,10 +3701,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>726865</v>
+        <v>726646</v>
       </c>
       <c r="R29" t="n">
-        <v>7354873</v>
+        <v>7355247</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>

--- a/artfynd/A 29675-2024 artfynd.xlsx
+++ b/artfynd/A 29675-2024 artfynd.xlsx
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121589896</v>
+        <v>121589871</v>
       </c>
       <c r="B3" t="n">
-        <v>78609</v>
+        <v>97059</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,25 +803,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -831,6 +831,7 @@
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -838,10 +839,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>726865</v>
+        <v>726939</v>
       </c>
       <c r="R3" t="n">
-        <v>7354873</v>
+        <v>7355544</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -901,10 +902,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121589882</v>
+        <v>121589893</v>
       </c>
       <c r="B4" t="n">
-        <v>78609</v>
+        <v>79719</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,25 +914,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -948,10 +949,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>726600</v>
+        <v>726716</v>
       </c>
       <c r="R4" t="n">
-        <v>7355553</v>
+        <v>7354943</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -978,12 +979,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1012,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121589871</v>
+        <v>121589902</v>
       </c>
       <c r="B5" t="n">
-        <v>97059</v>
+        <v>79594</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,21 +1028,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>6456</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1051,7 +1052,6 @@
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1059,10 +1059,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>726939</v>
+        <v>726867</v>
       </c>
       <c r="R5" t="n">
-        <v>7355544</v>
+        <v>7354803</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1122,10 +1122,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121589901</v>
+        <v>121589882</v>
       </c>
       <c r="B6" t="n">
-        <v>90738</v>
+        <v>78609</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1138,21 +1138,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1169,10 +1169,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>726863</v>
+        <v>726600</v>
       </c>
       <c r="R6" t="n">
-        <v>7354872</v>
+        <v>7355553</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1232,7 +1232,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121589890</v>
+        <v>121589877</v>
       </c>
       <c r="B7" t="n">
         <v>78609</v>
@@ -1279,10 +1279,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>726689</v>
+        <v>726675</v>
       </c>
       <c r="R7" t="n">
-        <v>7355064</v>
+        <v>7355240</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1342,10 +1342,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121589891</v>
+        <v>121589884</v>
       </c>
       <c r="B8" t="n">
-        <v>79726</v>
+        <v>78609</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1354,25 +1354,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>726725</v>
+        <v>726405</v>
       </c>
       <c r="R8" t="n">
-        <v>7354940</v>
+        <v>7355166</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1452,10 +1452,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121589876</v>
+        <v>121589897</v>
       </c>
       <c r="B9" t="n">
-        <v>82393</v>
+        <v>79718</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1464,25 +1464,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1312</v>
+        <v>6461</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1499,10 +1499,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>726693</v>
+        <v>726759</v>
       </c>
       <c r="R9" t="n">
-        <v>7355235</v>
+        <v>7354946</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1562,7 +1562,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121589899</v>
+        <v>121589876</v>
       </c>
       <c r="B10" t="n">
         <v>82393</v>
@@ -1609,10 +1609,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>726760</v>
+        <v>726693</v>
       </c>
       <c r="R10" t="n">
-        <v>7354944</v>
+        <v>7355235</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1639,12 +1639,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1672,10 +1672,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121589877</v>
+        <v>121589880</v>
       </c>
       <c r="B11" t="n">
-        <v>78609</v>
+        <v>91674</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1684,25 +1684,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>4787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granriska</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lactarius zonarioides</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Kühner &amp; Romagn.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1719,10 +1719,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>726675</v>
+        <v>726609</v>
       </c>
       <c r="R11" t="n">
-        <v>7355240</v>
+        <v>7355531</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1782,10 +1782,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121589884</v>
+        <v>121589879</v>
       </c>
       <c r="B12" t="n">
-        <v>78609</v>
+        <v>79718</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1794,25 +1794,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1829,10 +1829,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>726405</v>
+        <v>726622</v>
       </c>
       <c r="R12" t="n">
-        <v>7355166</v>
+        <v>7355532</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1892,10 +1892,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121589880</v>
+        <v>121589875</v>
       </c>
       <c r="B13" t="n">
-        <v>91674</v>
+        <v>79719</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1908,21 +1908,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4787</v>
+        <v>6462</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granriska</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lactarius zonarioides</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Kühner &amp; Romagn.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>726609</v>
+        <v>726667</v>
       </c>
       <c r="R13" t="n">
-        <v>7355531</v>
+        <v>7355228</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2002,10 +2002,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121589875</v>
+        <v>121589891</v>
       </c>
       <c r="B14" t="n">
-        <v>79719</v>
+        <v>79726</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2018,21 +2018,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6462</v>
+        <v>6464</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2049,10 +2049,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>726667</v>
+        <v>726725</v>
       </c>
       <c r="R14" t="n">
-        <v>7355228</v>
+        <v>7354940</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2222,10 +2222,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121589872</v>
+        <v>121589883</v>
       </c>
       <c r="B16" t="n">
-        <v>56568</v>
+        <v>78691</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2234,25 +2234,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100138</v>
+        <v>864</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2260,9 +2260,8 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2270,10 +2269,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>726920</v>
+        <v>726404</v>
       </c>
       <c r="R16" t="n">
-        <v>7355536</v>
+        <v>7355159</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2314,6 +2313,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2332,10 +2332,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121589874</v>
+        <v>121589878</v>
       </c>
       <c r="B17" t="n">
-        <v>78609</v>
+        <v>82393</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2348,21 +2348,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2379,10 +2379,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>726754</v>
+        <v>726646</v>
       </c>
       <c r="R17" t="n">
-        <v>7355194</v>
+        <v>7355247</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2442,10 +2442,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121589879</v>
+        <v>121589892</v>
       </c>
       <c r="B18" t="n">
-        <v>79718</v>
+        <v>78609</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2454,25 +2454,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2489,10 +2489,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>726622</v>
+        <v>726717</v>
       </c>
       <c r="R18" t="n">
-        <v>7355532</v>
+        <v>7354967</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2552,10 +2552,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121589895</v>
+        <v>121589901</v>
       </c>
       <c r="B19" t="n">
-        <v>97059</v>
+        <v>90738</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2564,25 +2564,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221945</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2592,7 +2592,6 @@
       </c>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2600,10 +2599,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>726866</v>
+        <v>726863</v>
       </c>
       <c r="R19" t="n">
-        <v>7354811</v>
+        <v>7354872</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2663,10 +2662,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121589883</v>
+        <v>121589899</v>
       </c>
       <c r="B20" t="n">
-        <v>78691</v>
+        <v>82393</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2679,21 +2678,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>864</v>
+        <v>1312</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2710,10 +2709,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>726404</v>
+        <v>726760</v>
       </c>
       <c r="R20" t="n">
-        <v>7355159</v>
+        <v>7354944</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2740,12 +2739,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2773,10 +2772,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121589881</v>
+        <v>121589872</v>
       </c>
       <c r="B21" t="n">
-        <v>97065</v>
+        <v>56568</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2789,21 +2788,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221941</v>
+        <v>100138</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2811,9 +2810,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2821,10 +2820,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>726603</v>
+        <v>726920</v>
       </c>
       <c r="R21" t="n">
-        <v>7355549</v>
+        <v>7355536</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2865,7 +2864,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2884,10 +2882,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121589898</v>
+        <v>121589873</v>
       </c>
       <c r="B22" t="n">
-        <v>91674</v>
+        <v>79719</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2900,21 +2898,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4787</v>
+        <v>6462</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granriska</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lactarius zonarioides</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Kühner &amp; Romagn.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2931,10 +2929,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>726741</v>
+        <v>726754</v>
       </c>
       <c r="R22" t="n">
-        <v>7354942</v>
+        <v>7355172</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2994,10 +2992,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121589897</v>
+        <v>121589896</v>
       </c>
       <c r="B23" t="n">
-        <v>79718</v>
+        <v>78609</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3006,25 +3004,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -3041,10 +3039,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>726759</v>
+        <v>726865</v>
       </c>
       <c r="R23" t="n">
-        <v>7354946</v>
+        <v>7354873</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3104,10 +3102,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121589893</v>
+        <v>121589890</v>
       </c>
       <c r="B24" t="n">
-        <v>79719</v>
+        <v>78609</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3116,25 +3114,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3151,10 +3149,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>726716</v>
+        <v>726689</v>
       </c>
       <c r="R24" t="n">
-        <v>7354943</v>
+        <v>7355064</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3181,12 +3179,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3214,10 +3212,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121589892</v>
+        <v>121589881</v>
       </c>
       <c r="B25" t="n">
-        <v>78609</v>
+        <v>97065</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3226,25 +3224,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3254,6 +3252,7 @@
       </c>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3261,10 +3260,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>726717</v>
+        <v>726603</v>
       </c>
       <c r="R25" t="n">
-        <v>7354967</v>
+        <v>7355549</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3324,10 +3323,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121589873</v>
+        <v>121589874</v>
       </c>
       <c r="B26" t="n">
-        <v>79719</v>
+        <v>78609</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3336,25 +3335,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3374,7 +3373,7 @@
         <v>726754</v>
       </c>
       <c r="R26" t="n">
-        <v>7355172</v>
+        <v>7355194</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3434,10 +3433,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121589900</v>
+        <v>121589898</v>
       </c>
       <c r="B27" t="n">
-        <v>78691</v>
+        <v>91674</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3446,25 +3445,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>864</v>
+        <v>4787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Granriska</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lactarius zonarioides</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>Kühner &amp; Romagn.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3481,10 +3480,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>726863</v>
+        <v>726741</v>
       </c>
       <c r="R27" t="n">
-        <v>7354860</v>
+        <v>7354942</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3511,12 +3510,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3544,10 +3543,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121589902</v>
+        <v>121589895</v>
       </c>
       <c r="B28" t="n">
-        <v>79594</v>
+        <v>97059</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3560,21 +3559,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6456</v>
+        <v>221945</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3584,6 +3583,7 @@
       </c>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3591,10 +3591,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>726867</v>
+        <v>726866</v>
       </c>
       <c r="R28" t="n">
-        <v>7354803</v>
+        <v>7354811</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3654,10 +3654,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121589878</v>
+        <v>121589900</v>
       </c>
       <c r="B29" t="n">
-        <v>82393</v>
+        <v>78691</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3670,21 +3670,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1312</v>
+        <v>864</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3701,10 +3701,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>726646</v>
+        <v>726863</v>
       </c>
       <c r="R29" t="n">
-        <v>7355247</v>
+        <v>7354860</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3731,12 +3731,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD29" t="b">

--- a/artfynd/A 29675-2024 artfynd.xlsx
+++ b/artfynd/A 29675-2024 artfynd.xlsx
@@ -1562,10 +1562,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121589876</v>
+        <v>121589880</v>
       </c>
       <c r="B10" t="n">
-        <v>82393</v>
+        <v>91674</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1574,25 +1574,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1312</v>
+        <v>4787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granriska</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lactarius zonarioides</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Kühner &amp; Romagn.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1609,10 +1609,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>726693</v>
+        <v>726609</v>
       </c>
       <c r="R10" t="n">
-        <v>7355235</v>
+        <v>7355531</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1672,10 +1672,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121589880</v>
+        <v>121589876</v>
       </c>
       <c r="B11" t="n">
-        <v>91674</v>
+        <v>82393</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1684,25 +1684,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4787</v>
+        <v>1312</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granriska</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lactarius zonarioides</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Kühner &amp; Romagn.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1719,10 +1719,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>726609</v>
+        <v>726693</v>
       </c>
       <c r="R11" t="n">
-        <v>7355531</v>
+        <v>7355235</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>

--- a/artfynd/A 29675-2024 artfynd.xlsx
+++ b/artfynd/A 29675-2024 artfynd.xlsx
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121589871</v>
+        <v>121589877</v>
       </c>
       <c r="B3" t="n">
-        <v>97059</v>
+        <v>78616</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,25 +803,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -831,7 +831,6 @@
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -839,10 +838,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>726939</v>
+        <v>726675</v>
       </c>
       <c r="R3" t="n">
-        <v>7355544</v>
+        <v>7355240</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -902,10 +901,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121589893</v>
+        <v>121589874</v>
       </c>
       <c r="B4" t="n">
-        <v>79719</v>
+        <v>78616</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -914,25 +913,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -949,10 +948,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>726716</v>
+        <v>726754</v>
       </c>
       <c r="R4" t="n">
-        <v>7354943</v>
+        <v>7355194</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -979,12 +978,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1012,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121589902</v>
+        <v>121589895</v>
       </c>
       <c r="B5" t="n">
-        <v>79594</v>
+        <v>97067</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1028,21 +1027,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6456</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1052,6 +1051,7 @@
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1059,10 +1059,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>726867</v>
+        <v>726866</v>
       </c>
       <c r="R5" t="n">
-        <v>7354803</v>
+        <v>7354811</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1122,10 +1122,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121589882</v>
+        <v>121589883</v>
       </c>
       <c r="B6" t="n">
-        <v>78609</v>
+        <v>78698</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1138,21 +1138,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1169,10 +1169,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>726600</v>
+        <v>726404</v>
       </c>
       <c r="R6" t="n">
-        <v>7355553</v>
+        <v>7355159</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1232,10 +1232,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121589877</v>
+        <v>121589902</v>
       </c>
       <c r="B7" t="n">
-        <v>78609</v>
+        <v>79601</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1244,25 +1244,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1279,10 +1279,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>726675</v>
+        <v>726867</v>
       </c>
       <c r="R7" t="n">
-        <v>7355240</v>
+        <v>7354803</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1342,10 +1342,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121589884</v>
+        <v>121589881</v>
       </c>
       <c r="B8" t="n">
-        <v>78609</v>
+        <v>97073</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1354,25 +1354,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1382,6 +1382,7 @@
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1389,10 +1390,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>726405</v>
+        <v>726603</v>
       </c>
       <c r="R8" t="n">
-        <v>7355166</v>
+        <v>7355549</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1452,10 +1453,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121589897</v>
+        <v>121589882</v>
       </c>
       <c r="B9" t="n">
-        <v>79718</v>
+        <v>78616</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1464,25 +1465,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1499,10 +1500,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>726759</v>
+        <v>726600</v>
       </c>
       <c r="R9" t="n">
-        <v>7354946</v>
+        <v>7355553</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1562,10 +1563,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121589880</v>
+        <v>121589900</v>
       </c>
       <c r="B10" t="n">
-        <v>91674</v>
+        <v>78698</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1574,25 +1575,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4787</v>
+        <v>864</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granriska</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lactarius zonarioides</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Kühner &amp; Romagn.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1609,10 +1610,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>726609</v>
+        <v>726863</v>
       </c>
       <c r="R10" t="n">
-        <v>7355531</v>
+        <v>7354860</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1639,12 +1640,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1672,10 +1673,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121589876</v>
+        <v>121589890</v>
       </c>
       <c r="B11" t="n">
-        <v>82393</v>
+        <v>78616</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1688,21 +1689,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1719,10 +1720,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>726693</v>
+        <v>726689</v>
       </c>
       <c r="R11" t="n">
-        <v>7355235</v>
+        <v>7355064</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1782,10 +1783,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121589879</v>
+        <v>121589892</v>
       </c>
       <c r="B12" t="n">
-        <v>79718</v>
+        <v>78616</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1794,25 +1795,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1829,10 +1830,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>726622</v>
+        <v>726717</v>
       </c>
       <c r="R12" t="n">
-        <v>7355532</v>
+        <v>7354967</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1892,10 +1893,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121589875</v>
+        <v>121589898</v>
       </c>
       <c r="B13" t="n">
-        <v>79719</v>
+        <v>91682</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1908,21 +1909,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6462</v>
+        <v>4787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granriska</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lactarius zonarioides</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Kühner &amp; Romagn.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1939,10 +1940,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>726667</v>
+        <v>726741</v>
       </c>
       <c r="R13" t="n">
-        <v>7355228</v>
+        <v>7354942</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2002,10 +2003,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121589891</v>
+        <v>121589899</v>
       </c>
       <c r="B14" t="n">
-        <v>79726</v>
+        <v>82400</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2014,25 +2015,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6464</v>
+        <v>1312</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2049,10 +2050,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>726725</v>
+        <v>726760</v>
       </c>
       <c r="R14" t="n">
-        <v>7354940</v>
+        <v>7354944</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2079,12 +2080,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2112,10 +2113,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121589894</v>
+        <v>121589896</v>
       </c>
       <c r="B15" t="n">
-        <v>79691</v>
+        <v>78616</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2128,21 +2129,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2159,10 +2160,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>726724</v>
+        <v>726865</v>
       </c>
       <c r="R15" t="n">
-        <v>7354941</v>
+        <v>7354873</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2222,10 +2223,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121589883</v>
+        <v>121589879</v>
       </c>
       <c r="B16" t="n">
-        <v>78691</v>
+        <v>79725</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2234,25 +2235,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>864</v>
+        <v>6461</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2269,10 +2270,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>726404</v>
+        <v>726622</v>
       </c>
       <c r="R16" t="n">
-        <v>7355159</v>
+        <v>7355532</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2332,10 +2333,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121589878</v>
+        <v>121589875</v>
       </c>
       <c r="B17" t="n">
-        <v>82393</v>
+        <v>79726</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2344,25 +2345,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1312</v>
+        <v>6462</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2379,10 +2380,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>726646</v>
+        <v>726667</v>
       </c>
       <c r="R17" t="n">
-        <v>7355247</v>
+        <v>7355228</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2442,10 +2443,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121589892</v>
+        <v>121589873</v>
       </c>
       <c r="B18" t="n">
-        <v>78609</v>
+        <v>79726</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2454,25 +2455,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2489,10 +2490,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>726717</v>
+        <v>726754</v>
       </c>
       <c r="R18" t="n">
-        <v>7354967</v>
+        <v>7355172</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2552,10 +2553,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121589901</v>
+        <v>121589876</v>
       </c>
       <c r="B19" t="n">
-        <v>90738</v>
+        <v>82400</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2568,21 +2569,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2599,10 +2600,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>726863</v>
+        <v>726693</v>
       </c>
       <c r="R19" t="n">
-        <v>7354872</v>
+        <v>7355235</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2662,10 +2663,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121589899</v>
+        <v>121589893</v>
       </c>
       <c r="B20" t="n">
-        <v>82393</v>
+        <v>79726</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2674,25 +2675,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1312</v>
+        <v>6462</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2709,10 +2710,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>726760</v>
+        <v>726716</v>
       </c>
       <c r="R20" t="n">
-        <v>7354944</v>
+        <v>7354943</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2772,10 +2773,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121589872</v>
+        <v>121589901</v>
       </c>
       <c r="B21" t="n">
-        <v>56568</v>
+        <v>90746</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2784,25 +2785,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100138</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2810,9 +2811,8 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2820,10 +2820,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>726920</v>
+        <v>726863</v>
       </c>
       <c r="R21" t="n">
-        <v>7355536</v>
+        <v>7354872</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2864,6 +2864,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2882,10 +2883,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121589873</v>
+        <v>121589880</v>
       </c>
       <c r="B22" t="n">
-        <v>79719</v>
+        <v>91682</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2898,21 +2899,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6462</v>
+        <v>4787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granriska</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lactarius zonarioides</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Kühner &amp; Romagn.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2929,10 +2930,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>726754</v>
+        <v>726609</v>
       </c>
       <c r="R22" t="n">
-        <v>7355172</v>
+        <v>7355531</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2992,10 +2993,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121589896</v>
+        <v>121589891</v>
       </c>
       <c r="B23" t="n">
-        <v>78609</v>
+        <v>79733</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3004,25 +3005,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -3039,10 +3040,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>726865</v>
+        <v>726725</v>
       </c>
       <c r="R23" t="n">
-        <v>7354873</v>
+        <v>7354940</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3102,10 +3103,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121589890</v>
+        <v>121589871</v>
       </c>
       <c r="B24" t="n">
-        <v>78609</v>
+        <v>97067</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3114,25 +3115,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3142,6 +3143,7 @@
       </c>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3149,10 +3151,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>726689</v>
+        <v>726939</v>
       </c>
       <c r="R24" t="n">
-        <v>7355064</v>
+        <v>7355544</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3212,10 +3214,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121589881</v>
+        <v>121589894</v>
       </c>
       <c r="B25" t="n">
-        <v>97065</v>
+        <v>79698</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3224,25 +3226,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221941</v>
+        <v>2081</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3252,7 +3254,6 @@
       </c>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3260,10 +3261,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>726603</v>
+        <v>726724</v>
       </c>
       <c r="R25" t="n">
-        <v>7355549</v>
+        <v>7354941</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3323,10 +3324,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121589874</v>
+        <v>121589872</v>
       </c>
       <c r="B26" t="n">
-        <v>78609</v>
+        <v>56569</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3335,25 +3336,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3361,8 +3362,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3370,10 +3372,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>726754</v>
+        <v>726920</v>
       </c>
       <c r="R26" t="n">
-        <v>7355194</v>
+        <v>7355536</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3414,7 +3416,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3433,10 +3434,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121589898</v>
+        <v>121589878</v>
       </c>
       <c r="B27" t="n">
-        <v>91674</v>
+        <v>82400</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3445,25 +3446,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4787</v>
+        <v>1312</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granriska</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lactarius zonarioides</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Kühner &amp; Romagn.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3480,10 +3481,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>726741</v>
+        <v>726646</v>
       </c>
       <c r="R27" t="n">
-        <v>7354942</v>
+        <v>7355247</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3543,10 +3544,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121589895</v>
+        <v>121589884</v>
       </c>
       <c r="B28" t="n">
-        <v>97059</v>
+        <v>78616</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3555,25 +3556,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3583,7 +3584,6 @@
       </c>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3591,10 +3591,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>726866</v>
+        <v>726405</v>
       </c>
       <c r="R28" t="n">
-        <v>7354811</v>
+        <v>7355166</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3654,10 +3654,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121589900</v>
+        <v>121589897</v>
       </c>
       <c r="B29" t="n">
-        <v>78691</v>
+        <v>79725</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3666,25 +3666,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>864</v>
+        <v>6461</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3701,10 +3701,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>726863</v>
+        <v>726759</v>
       </c>
       <c r="R29" t="n">
-        <v>7354860</v>
+        <v>7354946</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3731,12 +3731,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD29" t="b">

--- a/artfynd/A 29675-2024 artfynd.xlsx
+++ b/artfynd/A 29675-2024 artfynd.xlsx
@@ -2003,10 +2003,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121589899</v>
+        <v>121589896</v>
       </c>
       <c r="B14" t="n">
-        <v>82400</v>
+        <v>78616</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2019,21 +2019,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2050,10 +2050,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>726760</v>
+        <v>726865</v>
       </c>
       <c r="R14" t="n">
-        <v>7354944</v>
+        <v>7354873</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2080,12 +2080,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2113,10 +2113,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121589896</v>
+        <v>121589873</v>
       </c>
       <c r="B15" t="n">
-        <v>78616</v>
+        <v>79726</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2125,25 +2125,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2160,10 +2160,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>726865</v>
+        <v>726754</v>
       </c>
       <c r="R15" t="n">
-        <v>7354873</v>
+        <v>7355172</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2223,10 +2223,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121589879</v>
+        <v>121589899</v>
       </c>
       <c r="B16" t="n">
-        <v>79725</v>
+        <v>82400</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2235,25 +2235,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6461</v>
+        <v>1312</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2270,10 +2270,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>726622</v>
+        <v>726760</v>
       </c>
       <c r="R16" t="n">
-        <v>7355532</v>
+        <v>7354944</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2300,12 +2300,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2333,10 +2333,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121589875</v>
+        <v>121589879</v>
       </c>
       <c r="B17" t="n">
-        <v>79726</v>
+        <v>79725</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2349,21 +2349,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6462</v>
+        <v>6461</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2380,10 +2380,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>726667</v>
+        <v>726622</v>
       </c>
       <c r="R17" t="n">
-        <v>7355228</v>
+        <v>7355532</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2443,7 +2443,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121589873</v>
+        <v>121589875</v>
       </c>
       <c r="B18" t="n">
         <v>79726</v>
@@ -2490,10 +2490,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>726754</v>
+        <v>726667</v>
       </c>
       <c r="R18" t="n">
-        <v>7355172</v>
+        <v>7355228</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>

--- a/artfynd/A 29675-2024 artfynd.xlsx
+++ b/artfynd/A 29675-2024 artfynd.xlsx
@@ -2003,10 +2003,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121589896</v>
+        <v>121589899</v>
       </c>
       <c r="B14" t="n">
-        <v>78616</v>
+        <v>82400</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2019,21 +2019,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2050,10 +2050,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>726865</v>
+        <v>726760</v>
       </c>
       <c r="R14" t="n">
-        <v>7354873</v>
+        <v>7354944</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2080,12 +2080,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2113,10 +2113,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121589873</v>
+        <v>121589896</v>
       </c>
       <c r="B15" t="n">
-        <v>79726</v>
+        <v>78616</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2125,25 +2125,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2160,10 +2160,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>726754</v>
+        <v>726865</v>
       </c>
       <c r="R15" t="n">
-        <v>7355172</v>
+        <v>7354873</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2223,10 +2223,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121589899</v>
+        <v>121589879</v>
       </c>
       <c r="B16" t="n">
-        <v>82400</v>
+        <v>79725</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2235,25 +2235,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1312</v>
+        <v>6461</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2270,10 +2270,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>726760</v>
+        <v>726622</v>
       </c>
       <c r="R16" t="n">
-        <v>7354944</v>
+        <v>7355532</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2300,12 +2300,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2333,10 +2333,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121589879</v>
+        <v>121589875</v>
       </c>
       <c r="B17" t="n">
-        <v>79725</v>
+        <v>79726</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2349,21 +2349,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6461</v>
+        <v>6462</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2380,10 +2380,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>726622</v>
+        <v>726667</v>
       </c>
       <c r="R17" t="n">
-        <v>7355532</v>
+        <v>7355228</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2443,7 +2443,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121589875</v>
+        <v>121589873</v>
       </c>
       <c r="B18" t="n">
         <v>79726</v>
@@ -2490,10 +2490,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>726667</v>
+        <v>726754</v>
       </c>
       <c r="R18" t="n">
-        <v>7355228</v>
+        <v>7355172</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>

--- a/artfynd/A 29675-2024 artfynd.xlsx
+++ b/artfynd/A 29675-2024 artfynd.xlsx
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121589873</v>
+        <v>121589892</v>
       </c>
       <c r="B3" t="n">
-        <v>79726</v>
+        <v>78616</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,25 +803,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -838,10 +838,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>726754</v>
+        <v>726717</v>
       </c>
       <c r="R3" t="n">
-        <v>7355172</v>
+        <v>7354967</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -901,10 +901,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121589893</v>
+        <v>121589883</v>
       </c>
       <c r="B4" t="n">
-        <v>79726</v>
+        <v>78698</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,25 +913,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6462</v>
+        <v>864</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -948,10 +948,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>726716</v>
+        <v>726404</v>
       </c>
       <c r="R4" t="n">
-        <v>7354943</v>
+        <v>7355159</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -978,12 +978,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121589881</v>
+        <v>121589895</v>
       </c>
       <c r="B5" t="n">
-        <v>97073</v>
+        <v>97067</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,16 +1027,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221941</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1059,10 +1059,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>726603</v>
+        <v>726866</v>
       </c>
       <c r="R5" t="n">
-        <v>7355549</v>
+        <v>7354811</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1122,10 +1122,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121589883</v>
+        <v>121589876</v>
       </c>
       <c r="B6" t="n">
-        <v>78698</v>
+        <v>82400</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1138,21 +1138,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>864</v>
+        <v>1312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1169,10 +1169,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>726404</v>
+        <v>726693</v>
       </c>
       <c r="R6" t="n">
-        <v>7355159</v>
+        <v>7355235</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1232,10 +1232,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121589890</v>
+        <v>121589873</v>
       </c>
       <c r="B7" t="n">
-        <v>78616</v>
+        <v>79726</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1244,25 +1244,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1279,10 +1279,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>726689</v>
+        <v>726754</v>
       </c>
       <c r="R7" t="n">
-        <v>7355064</v>
+        <v>7355172</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1342,10 +1342,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121589884</v>
+        <v>121589902</v>
       </c>
       <c r="B8" t="n">
-        <v>78616</v>
+        <v>79601</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1354,25 +1354,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>726405</v>
+        <v>726867</v>
       </c>
       <c r="R8" t="n">
-        <v>7355166</v>
+        <v>7354803</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1452,10 +1452,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121589892</v>
+        <v>121589891</v>
       </c>
       <c r="B9" t="n">
-        <v>78616</v>
+        <v>79733</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1464,25 +1464,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1499,10 +1499,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>726717</v>
+        <v>726725</v>
       </c>
       <c r="R9" t="n">
-        <v>7354967</v>
+        <v>7354940</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1562,7 +1562,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121589882</v>
+        <v>121589884</v>
       </c>
       <c r="B10" t="n">
         <v>78616</v>
@@ -1609,10 +1609,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>726600</v>
+        <v>726405</v>
       </c>
       <c r="R10" t="n">
-        <v>7355553</v>
+        <v>7355166</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1672,10 +1672,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121589875</v>
+        <v>121589901</v>
       </c>
       <c r="B11" t="n">
-        <v>79726</v>
+        <v>90746</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1684,25 +1684,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1719,10 +1719,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>726667</v>
+        <v>726863</v>
       </c>
       <c r="R11" t="n">
-        <v>7355228</v>
+        <v>7354872</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1782,10 +1782,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121589902</v>
+        <v>121589879</v>
       </c>
       <c r="B12" t="n">
-        <v>79601</v>
+        <v>79725</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1798,21 +1798,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6456</v>
+        <v>6461</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1829,10 +1829,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>726867</v>
+        <v>726622</v>
       </c>
       <c r="R12" t="n">
-        <v>7354803</v>
+        <v>7355532</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1892,10 +1892,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121589894</v>
+        <v>121589872</v>
       </c>
       <c r="B13" t="n">
-        <v>79698</v>
+        <v>56569</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1904,25 +1904,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2081</v>
+        <v>100138</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1930,8 +1930,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1939,10 +1940,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>726724</v>
+        <v>726920</v>
       </c>
       <c r="R13" t="n">
-        <v>7354941</v>
+        <v>7355536</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1983,7 +1984,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2002,10 +2002,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121589880</v>
+        <v>121589899</v>
       </c>
       <c r="B14" t="n">
-        <v>91682</v>
+        <v>82400</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2014,25 +2014,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4787</v>
+        <v>1312</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granriska</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lactarius zonarioides</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Kühner &amp; Romagn.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2049,10 +2049,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>726609</v>
+        <v>726760</v>
       </c>
       <c r="R14" t="n">
-        <v>7355531</v>
+        <v>7354944</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2079,12 +2079,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2112,10 +2112,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121589896</v>
+        <v>121589880</v>
       </c>
       <c r="B15" t="n">
-        <v>78616</v>
+        <v>91682</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2124,25 +2124,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>4787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granriska</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lactarius zonarioides</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Kühner &amp; Romagn.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2159,10 +2159,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>726865</v>
+        <v>726609</v>
       </c>
       <c r="R15" t="n">
-        <v>7354873</v>
+        <v>7355531</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2222,10 +2222,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121589897</v>
+        <v>121589881</v>
       </c>
       <c r="B16" t="n">
-        <v>79725</v>
+        <v>97073</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2238,21 +2238,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6461</v>
+        <v>221941</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2262,6 +2262,7 @@
       </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2269,10 +2270,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>726759</v>
+        <v>726603</v>
       </c>
       <c r="R16" t="n">
-        <v>7354946</v>
+        <v>7355549</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2332,10 +2333,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121589895</v>
+        <v>121589875</v>
       </c>
       <c r="B17" t="n">
-        <v>97067</v>
+        <v>79726</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2348,21 +2349,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221945</v>
+        <v>6462</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2372,7 +2373,6 @@
       </c>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2380,10 +2380,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>726866</v>
+        <v>726667</v>
       </c>
       <c r="R17" t="n">
-        <v>7354811</v>
+        <v>7355228</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2443,10 +2443,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121589878</v>
+        <v>121589900</v>
       </c>
       <c r="B18" t="n">
-        <v>82400</v>
+        <v>78698</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2459,21 +2459,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1312</v>
+        <v>864</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2490,10 +2490,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>726646</v>
+        <v>726863</v>
       </c>
       <c r="R18" t="n">
-        <v>7355247</v>
+        <v>7354860</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2520,12 +2520,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2553,10 +2553,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121589872</v>
+        <v>121589882</v>
       </c>
       <c r="B19" t="n">
-        <v>56569</v>
+        <v>78616</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2565,25 +2565,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2591,9 +2591,8 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2601,10 +2600,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>726920</v>
+        <v>726600</v>
       </c>
       <c r="R19" t="n">
-        <v>7355536</v>
+        <v>7355553</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2645,6 +2644,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2663,10 +2663,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121589899</v>
+        <v>121589890</v>
       </c>
       <c r="B20" t="n">
-        <v>82400</v>
+        <v>78616</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2679,21 +2679,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2710,10 +2710,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>726760</v>
+        <v>726689</v>
       </c>
       <c r="R20" t="n">
-        <v>7354944</v>
+        <v>7355064</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2740,12 +2740,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2773,10 +2773,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121589871</v>
+        <v>121589893</v>
       </c>
       <c r="B21" t="n">
-        <v>97067</v>
+        <v>79726</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2789,21 +2789,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221945</v>
+        <v>6462</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2813,7 +2813,6 @@
       </c>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2821,10 +2820,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>726939</v>
+        <v>726716</v>
       </c>
       <c r="R21" t="n">
-        <v>7355544</v>
+        <v>7354943</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2851,12 +2850,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2884,10 +2883,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121589876</v>
+        <v>121589894</v>
       </c>
       <c r="B22" t="n">
-        <v>82400</v>
+        <v>79698</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2900,21 +2899,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1312</v>
+        <v>2081</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2931,10 +2930,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>726693</v>
+        <v>726724</v>
       </c>
       <c r="R22" t="n">
-        <v>7355235</v>
+        <v>7354941</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2994,10 +2993,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121589901</v>
+        <v>121589874</v>
       </c>
       <c r="B23" t="n">
-        <v>90746</v>
+        <v>78616</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3010,21 +3009,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -3041,10 +3040,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>726863</v>
+        <v>726754</v>
       </c>
       <c r="R23" t="n">
-        <v>7354872</v>
+        <v>7355194</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3104,10 +3103,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121589877</v>
+        <v>121589871</v>
       </c>
       <c r="B24" t="n">
-        <v>78616</v>
+        <v>97067</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3116,25 +3115,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3144,6 +3143,7 @@
       </c>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3151,10 +3151,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>726675</v>
+        <v>726939</v>
       </c>
       <c r="R24" t="n">
-        <v>7355240</v>
+        <v>7355544</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3214,7 +3214,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121589874</v>
+        <v>121589896</v>
       </c>
       <c r="B25" t="n">
         <v>78616</v>
@@ -3261,10 +3261,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>726754</v>
+        <v>726865</v>
       </c>
       <c r="R25" t="n">
-        <v>7355194</v>
+        <v>7354873</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3324,10 +3324,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121589879</v>
+        <v>121589898</v>
       </c>
       <c r="B26" t="n">
-        <v>79725</v>
+        <v>91682</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3340,21 +3340,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6461</v>
+        <v>4787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Granriska</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lactarius zonarioides</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>Kühner &amp; Romagn.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3371,10 +3371,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>726622</v>
+        <v>726741</v>
       </c>
       <c r="R26" t="n">
-        <v>7355532</v>
+        <v>7354942</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3434,10 +3434,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121589891</v>
+        <v>121589897</v>
       </c>
       <c r="B27" t="n">
-        <v>79733</v>
+        <v>79725</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3450,21 +3450,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6464</v>
+        <v>6461</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3481,10 +3481,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>726725</v>
+        <v>726759</v>
       </c>
       <c r="R27" t="n">
-        <v>7354940</v>
+        <v>7354946</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3544,10 +3544,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121589900</v>
+        <v>121589878</v>
       </c>
       <c r="B28" t="n">
-        <v>78698</v>
+        <v>82400</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3560,21 +3560,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>864</v>
+        <v>1312</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3591,10 +3591,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>726863</v>
+        <v>726646</v>
       </c>
       <c r="R28" t="n">
-        <v>7354860</v>
+        <v>7355247</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3621,12 +3621,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3654,10 +3654,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121589898</v>
+        <v>121589877</v>
       </c>
       <c r="B29" t="n">
-        <v>91682</v>
+        <v>78616</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3666,25 +3666,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4787</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granriska</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lactarius zonarioides</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Kühner &amp; Romagn.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3701,10 +3701,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>726741</v>
+        <v>726675</v>
       </c>
       <c r="R29" t="n">
-        <v>7354942</v>
+        <v>7355240</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>

--- a/artfynd/A 29675-2024 artfynd.xlsx
+++ b/artfynd/A 29675-2024 artfynd.xlsx
@@ -1122,10 +1122,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121589876</v>
+        <v>121589873</v>
       </c>
       <c r="B6" t="n">
-        <v>82400</v>
+        <v>79726</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1134,25 +1134,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1312</v>
+        <v>6462</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1169,10 +1169,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>726693</v>
+        <v>726754</v>
       </c>
       <c r="R6" t="n">
-        <v>7355235</v>
+        <v>7355172</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1232,10 +1232,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121589873</v>
+        <v>121589876</v>
       </c>
       <c r="B7" t="n">
-        <v>79726</v>
+        <v>82400</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1244,25 +1244,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6462</v>
+        <v>1312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1279,10 +1279,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>726754</v>
+        <v>726693</v>
       </c>
       <c r="R7" t="n">
-        <v>7355172</v>
+        <v>7355235</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1892,10 +1892,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121589872</v>
+        <v>121589880</v>
       </c>
       <c r="B13" t="n">
-        <v>56569</v>
+        <v>91682</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1908,21 +1908,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100138</v>
+        <v>4787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Granriska</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lactarius zonarioides</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Kühner &amp; Romagn.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1930,9 +1930,8 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1940,10 +1939,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>726920</v>
+        <v>726609</v>
       </c>
       <c r="R13" t="n">
-        <v>7355536</v>
+        <v>7355531</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1984,6 +1983,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2002,10 +2002,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121589899</v>
+        <v>121589872</v>
       </c>
       <c r="B14" t="n">
-        <v>82400</v>
+        <v>56569</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2014,25 +2014,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1312</v>
+        <v>100138</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2040,8 +2040,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2049,10 +2050,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>726760</v>
+        <v>726920</v>
       </c>
       <c r="R14" t="n">
-        <v>7354944</v>
+        <v>7355536</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2079,12 +2080,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2093,7 +2094,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2112,10 +2112,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121589880</v>
+        <v>121589899</v>
       </c>
       <c r="B15" t="n">
-        <v>91682</v>
+        <v>82400</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2124,25 +2124,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4787</v>
+        <v>1312</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granriska</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lactarius zonarioides</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Kühner &amp; Romagn.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2159,10 +2159,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>726609</v>
+        <v>726760</v>
       </c>
       <c r="R15" t="n">
-        <v>7355531</v>
+        <v>7354944</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2189,12 +2189,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2663,10 +2663,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121589890</v>
+        <v>121589893</v>
       </c>
       <c r="B20" t="n">
-        <v>78616</v>
+        <v>79726</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2675,25 +2675,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2710,10 +2710,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>726689</v>
+        <v>726716</v>
       </c>
       <c r="R20" t="n">
-        <v>7355064</v>
+        <v>7354943</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2740,12 +2740,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2773,10 +2773,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121589893</v>
+        <v>121589890</v>
       </c>
       <c r="B21" t="n">
-        <v>79726</v>
+        <v>78616</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2785,25 +2785,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2820,10 +2820,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>726716</v>
+        <v>726689</v>
       </c>
       <c r="R21" t="n">
-        <v>7354943</v>
+        <v>7355064</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2850,12 +2850,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3324,10 +3324,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121589898</v>
+        <v>121589897</v>
       </c>
       <c r="B26" t="n">
-        <v>91682</v>
+        <v>79725</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3340,21 +3340,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4787</v>
+        <v>6461</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granriska</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lactarius zonarioides</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Kühner &amp; Romagn.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3371,10 +3371,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>726741</v>
+        <v>726759</v>
       </c>
       <c r="R26" t="n">
-        <v>7354942</v>
+        <v>7354946</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3434,10 +3434,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121589897</v>
+        <v>121589898</v>
       </c>
       <c r="B27" t="n">
-        <v>79725</v>
+        <v>91682</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3450,21 +3450,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6461</v>
+        <v>4787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Granriska</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lactarius zonarioides</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>Kühner &amp; Romagn.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3481,10 +3481,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>726759</v>
+        <v>726741</v>
       </c>
       <c r="R27" t="n">
-        <v>7354946</v>
+        <v>7354942</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>

--- a/artfynd/A 29675-2024 artfynd.xlsx
+++ b/artfynd/A 29675-2024 artfynd.xlsx
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121589892</v>
+        <v>121589902</v>
       </c>
       <c r="B3" t="n">
-        <v>78616</v>
+        <v>79601</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,25 +803,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -838,10 +838,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>726717</v>
+        <v>726867</v>
       </c>
       <c r="R3" t="n">
-        <v>7354967</v>
+        <v>7354803</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -901,10 +901,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121589883</v>
+        <v>121589882</v>
       </c>
       <c r="B4" t="n">
-        <v>78698</v>
+        <v>78616</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -917,21 +917,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -948,10 +948,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>726404</v>
+        <v>726600</v>
       </c>
       <c r="R4" t="n">
-        <v>7355159</v>
+        <v>7355553</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121589895</v>
+        <v>121589891</v>
       </c>
       <c r="B5" t="n">
-        <v>97067</v>
+        <v>79733</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,21 +1027,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>6464</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1051,7 +1051,6 @@
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1059,10 +1058,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>726866</v>
+        <v>726725</v>
       </c>
       <c r="R5" t="n">
-        <v>7354811</v>
+        <v>7354940</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1122,10 +1121,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121589873</v>
+        <v>121589897</v>
       </c>
       <c r="B6" t="n">
-        <v>79726</v>
+        <v>79725</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1138,21 +1137,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6462</v>
+        <v>6461</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1169,10 +1168,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>726754</v>
+        <v>726759</v>
       </c>
       <c r="R6" t="n">
-        <v>7355172</v>
+        <v>7354946</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1232,10 +1231,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121589876</v>
+        <v>121589875</v>
       </c>
       <c r="B7" t="n">
-        <v>82400</v>
+        <v>79726</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1244,25 +1243,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1312</v>
+        <v>6462</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1279,10 +1278,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>726693</v>
+        <v>726667</v>
       </c>
       <c r="R7" t="n">
-        <v>7355235</v>
+        <v>7355228</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1342,10 +1341,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121589902</v>
+        <v>121589873</v>
       </c>
       <c r="B8" t="n">
-        <v>79601</v>
+        <v>79726</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1358,21 +1357,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6456</v>
+        <v>6462</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1389,10 +1388,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>726867</v>
+        <v>726754</v>
       </c>
       <c r="R8" t="n">
-        <v>7354803</v>
+        <v>7355172</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1452,10 +1451,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121589891</v>
+        <v>121589872</v>
       </c>
       <c r="B9" t="n">
-        <v>79733</v>
+        <v>56569</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1468,21 +1467,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6464</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1490,8 +1489,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1499,10 +1499,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>726725</v>
+        <v>726920</v>
       </c>
       <c r="R9" t="n">
-        <v>7354940</v>
+        <v>7355536</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1543,7 +1543,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1562,10 +1561,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121589884</v>
+        <v>121589883</v>
       </c>
       <c r="B10" t="n">
-        <v>78616</v>
+        <v>78698</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1578,21 +1577,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1609,10 +1608,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>726405</v>
+        <v>726404</v>
       </c>
       <c r="R10" t="n">
-        <v>7355166</v>
+        <v>7355159</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1672,10 +1671,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121589901</v>
+        <v>121589893</v>
       </c>
       <c r="B11" t="n">
-        <v>90746</v>
+        <v>79726</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1684,25 +1683,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1719,10 +1718,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>726863</v>
+        <v>726716</v>
       </c>
       <c r="R11" t="n">
-        <v>7354872</v>
+        <v>7354943</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1749,12 +1748,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1782,10 +1781,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121589879</v>
+        <v>121589896</v>
       </c>
       <c r="B12" t="n">
-        <v>79725</v>
+        <v>78616</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1794,25 +1793,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1829,10 +1828,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>726622</v>
+        <v>726865</v>
       </c>
       <c r="R12" t="n">
-        <v>7355532</v>
+        <v>7354873</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1892,10 +1891,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121589880</v>
+        <v>121589901</v>
       </c>
       <c r="B13" t="n">
-        <v>91682</v>
+        <v>90746</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1904,25 +1903,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4787</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granriska</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lactarius zonarioides</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Kühner &amp; Romagn.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1939,10 +1938,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>726609</v>
+        <v>726863</v>
       </c>
       <c r="R13" t="n">
-        <v>7355531</v>
+        <v>7354872</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2002,10 +2001,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121589872</v>
+        <v>121589884</v>
       </c>
       <c r="B14" t="n">
-        <v>56569</v>
+        <v>78616</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2014,25 +2013,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2040,9 +2039,8 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2050,10 +2048,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>726920</v>
+        <v>726405</v>
       </c>
       <c r="R14" t="n">
-        <v>7355536</v>
+        <v>7355166</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2094,6 +2092,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2112,10 +2111,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121589899</v>
+        <v>121589890</v>
       </c>
       <c r="B15" t="n">
-        <v>82400</v>
+        <v>78616</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2128,21 +2127,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2159,10 +2158,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>726760</v>
+        <v>726689</v>
       </c>
       <c r="R15" t="n">
-        <v>7354944</v>
+        <v>7355064</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2189,12 +2188,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2222,10 +2221,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121589881</v>
+        <v>121589877</v>
       </c>
       <c r="B16" t="n">
-        <v>97073</v>
+        <v>78616</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2234,25 +2233,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2262,7 +2261,6 @@
       </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2270,10 +2268,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>726603</v>
+        <v>726675</v>
       </c>
       <c r="R16" t="n">
-        <v>7355549</v>
+        <v>7355240</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2333,10 +2331,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121589875</v>
+        <v>121589874</v>
       </c>
       <c r="B17" t="n">
-        <v>79726</v>
+        <v>78616</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2345,25 +2343,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2380,10 +2378,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>726667</v>
+        <v>726754</v>
       </c>
       <c r="R17" t="n">
-        <v>7355228</v>
+        <v>7355194</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2443,10 +2441,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121589900</v>
+        <v>121589881</v>
       </c>
       <c r="B18" t="n">
-        <v>78698</v>
+        <v>97073</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2455,25 +2453,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>864</v>
+        <v>221941</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2483,6 +2481,7 @@
       </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2490,10 +2489,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>726863</v>
+        <v>726603</v>
       </c>
       <c r="R18" t="n">
-        <v>7354860</v>
+        <v>7355549</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2520,12 +2519,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2553,10 +2552,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121589882</v>
+        <v>121589894</v>
       </c>
       <c r="B19" t="n">
-        <v>78616</v>
+        <v>79698</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2569,21 +2568,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2600,10 +2599,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>726600</v>
+        <v>726724</v>
       </c>
       <c r="R19" t="n">
-        <v>7355553</v>
+        <v>7354941</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2663,10 +2662,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121589893</v>
+        <v>121589900</v>
       </c>
       <c r="B20" t="n">
-        <v>79726</v>
+        <v>78698</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2675,25 +2674,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6462</v>
+        <v>864</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2710,10 +2709,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>726716</v>
+        <v>726863</v>
       </c>
       <c r="R20" t="n">
-        <v>7354943</v>
+        <v>7354860</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2773,7 +2772,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121589890</v>
+        <v>121589892</v>
       </c>
       <c r="B21" t="n">
         <v>78616</v>
@@ -2820,10 +2819,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>726689</v>
+        <v>726717</v>
       </c>
       <c r="R21" t="n">
-        <v>7355064</v>
+        <v>7354967</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2883,10 +2882,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121589894</v>
+        <v>121589876</v>
       </c>
       <c r="B22" t="n">
-        <v>79698</v>
+        <v>82400</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2899,21 +2898,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2081</v>
+        <v>1312</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2930,10 +2929,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>726724</v>
+        <v>726693</v>
       </c>
       <c r="R22" t="n">
-        <v>7354941</v>
+        <v>7355235</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2993,10 +2992,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121589874</v>
+        <v>121589898</v>
       </c>
       <c r="B23" t="n">
-        <v>78616</v>
+        <v>91682</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3005,25 +3004,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>4787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granriska</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lactarius zonarioides</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Kühner &amp; Romagn.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -3040,10 +3039,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>726754</v>
+        <v>726741</v>
       </c>
       <c r="R23" t="n">
-        <v>7355194</v>
+        <v>7354942</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3103,10 +3102,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121589871</v>
+        <v>121589880</v>
       </c>
       <c r="B24" t="n">
-        <v>97067</v>
+        <v>91682</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3119,21 +3118,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221945</v>
+        <v>4787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Granriska</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lactarius zonarioides</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Kühner &amp; Romagn.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3143,7 +3142,6 @@
       </c>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3151,10 +3149,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>726939</v>
+        <v>726609</v>
       </c>
       <c r="R24" t="n">
-        <v>7355544</v>
+        <v>7355531</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3214,10 +3212,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121589896</v>
+        <v>121589878</v>
       </c>
       <c r="B25" t="n">
-        <v>78616</v>
+        <v>82400</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3230,21 +3228,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3261,10 +3259,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>726865</v>
+        <v>726646</v>
       </c>
       <c r="R25" t="n">
-        <v>7354873</v>
+        <v>7355247</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3324,7 +3322,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121589897</v>
+        <v>121589879</v>
       </c>
       <c r="B26" t="n">
         <v>79725</v>
@@ -3371,10 +3369,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>726759</v>
+        <v>726622</v>
       </c>
       <c r="R26" t="n">
-        <v>7354946</v>
+        <v>7355532</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3434,10 +3432,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121589898</v>
+        <v>121589899</v>
       </c>
       <c r="B27" t="n">
-        <v>91682</v>
+        <v>82400</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3446,25 +3444,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4787</v>
+        <v>1312</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granriska</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lactarius zonarioides</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Kühner &amp; Romagn.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3481,10 +3479,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>726741</v>
+        <v>726760</v>
       </c>
       <c r="R27" t="n">
-        <v>7354942</v>
+        <v>7354944</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3511,12 +3509,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3544,10 +3542,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121589878</v>
+        <v>121589871</v>
       </c>
       <c r="B28" t="n">
-        <v>82400</v>
+        <v>97067</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3556,25 +3554,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1312</v>
+        <v>221945</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3584,6 +3582,7 @@
       </c>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3591,10 +3590,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>726646</v>
+        <v>726939</v>
       </c>
       <c r="R28" t="n">
-        <v>7355247</v>
+        <v>7355544</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3654,10 +3653,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121589877</v>
+        <v>121589895</v>
       </c>
       <c r="B29" t="n">
-        <v>78616</v>
+        <v>97067</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3666,25 +3665,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3694,6 +3693,7 @@
       </c>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3701,10 +3701,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>726675</v>
+        <v>726866</v>
       </c>
       <c r="R29" t="n">
-        <v>7355240</v>
+        <v>7354811</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>

--- a/artfynd/A 29675-2024 artfynd.xlsx
+++ b/artfynd/A 29675-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY29"/>
+  <dimension ref="A1:AY30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3762,6 +3762,103 @@
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>126315540</v>
+      </c>
+      <c r="B30" t="n">
+        <v>79040</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>637</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Ringlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Evernia divaricata</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Sadimoajvve, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>726992</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7355076</v>
+      </c>
+      <c r="S30" t="n">
+        <v>20</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 29675-2024 artfynd.xlsx
+++ b/artfynd/A 29675-2024 artfynd.xlsx
@@ -3767,7 +3767,7 @@
         <v>126315540</v>
       </c>
       <c r="B30" t="n">
-        <v>79040</v>
+        <v>79044</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 29675-2024 artfynd.xlsx
+++ b/artfynd/A 29675-2024 artfynd.xlsx
@@ -3767,7 +3767,7 @@
         <v>126315540</v>
       </c>
       <c r="B30" t="n">
-        <v>79044</v>
+        <v>79047</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 29675-2024 artfynd.xlsx
+++ b/artfynd/A 29675-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121127723</v>
       </c>
       <c r="B2" t="n">
-        <v>80217</v>
+        <v>80218</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 29675-2024 artfynd.xlsx
+++ b/artfynd/A 29675-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121127723</v>
       </c>
       <c r="B2" t="n">
-        <v>80218</v>
+        <v>80220</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 29675-2024 artfynd.xlsx
+++ b/artfynd/A 29675-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121127723</v>
       </c>
       <c r="B2" t="n">
-        <v>80220</v>
+        <v>80221</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 29675-2024 artfynd.xlsx
+++ b/artfynd/A 29675-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121127723</v>
       </c>
       <c r="B2" t="n">
-        <v>80221</v>
+        <v>80222</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 29675-2024 artfynd.xlsx
+++ b/artfynd/A 29675-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY30"/>
+  <dimension ref="A1:AY33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>121127723</v>
       </c>
       <c r="B2" t="n">
-        <v>80222</v>
+        <v>80299</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -786,60 +786,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121589898</v>
+        <v>126315540</v>
       </c>
       <c r="B3" t="n">
-        <v>91696</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79394</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4787</v>
+        <v>637</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granriska</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lactarius zonarioides</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Kühner &amp; Romagn.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Jokkmokksmyran, Lu lm</t>
+          <t>Sadimoajvve, Lu lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>726741</v>
+        <v>726992</v>
       </c>
       <c r="R3" t="n">
-        <v>7354942</v>
+        <v>7355076</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -877,7 +865,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -896,15 +883,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121589877</v>
+        <v>121589883</v>
       </c>
       <c r="B4" t="n">
-        <v>78629</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -912,21 +894,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -943,10 +925,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>726675</v>
+        <v>726404</v>
       </c>
       <c r="R4" t="n">
-        <v>7355240</v>
+        <v>7355159</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1006,15 +988,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121589882</v>
+        <v>121589888</v>
       </c>
       <c r="B5" t="n">
-        <v>78629</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1022,21 +999,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1053,10 +1030,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>726600</v>
+        <v>726340</v>
       </c>
       <c r="R5" t="n">
-        <v>7355553</v>
+        <v>7355217</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1116,15 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121589874</v>
+        <v>121589900</v>
       </c>
       <c r="B6" t="n">
-        <v>78629</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1132,21 +1104,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1163,10 +1135,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>726754</v>
+        <v>726863</v>
       </c>
       <c r="R6" t="n">
-        <v>7355194</v>
+        <v>7354860</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1193,12 +1165,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1226,37 +1198,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121589873</v>
+        <v>121589876</v>
       </c>
       <c r="B7" t="n">
-        <v>79739</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6462</v>
+        <v>1312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1273,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>726754</v>
+        <v>726693</v>
       </c>
       <c r="R7" t="n">
-        <v>7355172</v>
+        <v>7355235</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1336,37 +1303,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121589879</v>
+        <v>121589878</v>
       </c>
       <c r="B8" t="n">
-        <v>79738</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6461</v>
+        <v>1312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1383,10 +1345,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>726622</v>
+        <v>726646</v>
       </c>
       <c r="R8" t="n">
-        <v>7355532</v>
+        <v>7355247</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1446,15 +1408,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121589883</v>
+        <v>121589885</v>
       </c>
       <c r="B9" t="n">
-        <v>78711</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1462,21 +1419,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>864</v>
+        <v>1312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1493,10 +1450,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>726404</v>
+        <v>726361</v>
       </c>
       <c r="R9" t="n">
-        <v>7355159</v>
+        <v>7355124</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1556,15 +1513,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121589900</v>
+        <v>121589899</v>
       </c>
       <c r="B10" t="n">
-        <v>78711</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1572,21 +1524,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>864</v>
+        <v>1312</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1603,10 +1555,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>726863</v>
+        <v>726760</v>
       </c>
       <c r="R10" t="n">
-        <v>7354860</v>
+        <v>7354944</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1669,12 +1621,7 @@
         <v>121589894</v>
       </c>
       <c r="B11" t="n">
-        <v>79711</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1776,15 +1723,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121589871</v>
+        <v>121589880</v>
       </c>
       <c r="B12" t="n">
-        <v>97085</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92886</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1792,21 +1734,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221945</v>
+        <v>4787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Granriska</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lactarius zonarioides</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Kühner &amp; Romagn.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1816,7 +1758,6 @@
       </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1824,10 +1765,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>726939</v>
+        <v>726609</v>
       </c>
       <c r="R12" t="n">
-        <v>7355544</v>
+        <v>7355531</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1887,15 +1828,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121589881</v>
+        <v>121589898</v>
       </c>
       <c r="B13" t="n">
-        <v>97091</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92886</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1903,21 +1839,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221941</v>
+        <v>4787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Granriska</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Lactarius zonarioides</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Kühner &amp; Romagn.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1927,7 +1863,6 @@
       </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1935,10 +1870,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>726603</v>
+        <v>726741</v>
       </c>
       <c r="R13" t="n">
-        <v>7355549</v>
+        <v>7354942</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1998,37 +1933,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121589876</v>
+        <v>121589874</v>
       </c>
       <c r="B14" t="n">
-        <v>82414</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2045,10 +1975,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>726693</v>
+        <v>726754</v>
       </c>
       <c r="R14" t="n">
-        <v>7355235</v>
+        <v>7355194</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2108,37 +2038,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121589878</v>
+        <v>121589877</v>
       </c>
       <c r="B15" t="n">
-        <v>82414</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2155,10 +2080,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>726646</v>
+        <v>726675</v>
       </c>
       <c r="R15" t="n">
-        <v>7355247</v>
+        <v>7355240</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2218,19 +2143,14 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121589884</v>
+        <v>121589882</v>
       </c>
       <c r="B16" t="n">
-        <v>78629</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2265,10 +2185,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>726405</v>
+        <v>726600</v>
       </c>
       <c r="R16" t="n">
-        <v>7355166</v>
+        <v>7355553</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2328,37 +2248,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121589897</v>
+        <v>121589884</v>
       </c>
       <c r="B17" t="n">
-        <v>79738</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2375,10 +2290,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>726759</v>
+        <v>726405</v>
       </c>
       <c r="R17" t="n">
-        <v>7354946</v>
+        <v>7355166</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2438,37 +2353,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121589891</v>
+        <v>121589886</v>
       </c>
       <c r="B18" t="n">
-        <v>79746</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2485,10 +2395,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>726725</v>
+        <v>726360</v>
       </c>
       <c r="R18" t="n">
-        <v>7354940</v>
+        <v>7355118</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2548,37 +2458,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121589902</v>
+        <v>121589887</v>
       </c>
       <c r="B19" t="n">
-        <v>79614</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2595,10 +2500,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>726867</v>
+        <v>726326</v>
       </c>
       <c r="R19" t="n">
-        <v>7354803</v>
+        <v>7355209</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2658,37 +2563,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121589875</v>
+        <v>121589890</v>
       </c>
       <c r="B20" t="n">
-        <v>79739</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2705,10 +2605,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>726667</v>
+        <v>726689</v>
       </c>
       <c r="R20" t="n">
-        <v>7355228</v>
+        <v>7355064</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2768,37 +2668,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121589880</v>
+        <v>121589892</v>
       </c>
       <c r="B21" t="n">
-        <v>91696</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4787</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granriska</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lactarius zonarioides</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Kühner &amp; Romagn.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2815,10 +2710,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>726609</v>
+        <v>726717</v>
       </c>
       <c r="R21" t="n">
-        <v>7355531</v>
+        <v>7354967</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2878,19 +2773,14 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121589890</v>
+        <v>121589896</v>
       </c>
       <c r="B22" t="n">
-        <v>78629</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -2925,10 +2815,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>726689</v>
+        <v>726865</v>
       </c>
       <c r="R22" t="n">
-        <v>7355064</v>
+        <v>7354873</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2988,15 +2878,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121589872</v>
+        <v>121589902</v>
       </c>
       <c r="B23" t="n">
-        <v>56577</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3004,21 +2889,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100138</v>
+        <v>6456</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -3026,9 +2911,8 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3036,10 +2920,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>726920</v>
+        <v>726867</v>
       </c>
       <c r="R23" t="n">
-        <v>7355536</v>
+        <v>7354803</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3080,6 +2964,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3098,15 +2983,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121589895</v>
+        <v>121589879</v>
       </c>
       <c r="B24" t="n">
-        <v>97085</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80460</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3114,21 +2994,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221945</v>
+        <v>6461</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3138,7 +3018,6 @@
       </c>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3146,10 +3025,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>726866</v>
+        <v>726622</v>
       </c>
       <c r="R24" t="n">
-        <v>7354811</v>
+        <v>7355532</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3209,37 +3088,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121589899</v>
+        <v>121589897</v>
       </c>
       <c r="B25" t="n">
-        <v>82414</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80460</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1312</v>
+        <v>6461</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3256,10 +3130,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>726760</v>
+        <v>726759</v>
       </c>
       <c r="R25" t="n">
-        <v>7354944</v>
+        <v>7354946</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3286,12 +3160,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3319,37 +3193,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121589896</v>
+        <v>121589873</v>
       </c>
       <c r="B26" t="n">
-        <v>78629</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3366,10 +3235,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>726865</v>
+        <v>726754</v>
       </c>
       <c r="R26" t="n">
-        <v>7354873</v>
+        <v>7355172</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3429,15 +3298,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121589893</v>
+        <v>121589875</v>
       </c>
       <c r="B27" t="n">
-        <v>79739</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3476,10 +3340,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>726716</v>
+        <v>726667</v>
       </c>
       <c r="R27" t="n">
-        <v>7354943</v>
+        <v>7355228</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3506,12 +3370,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3539,37 +3403,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121589901</v>
+        <v>121589893</v>
       </c>
       <c r="B28" t="n">
-        <v>90760</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3586,10 +3445,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>726863</v>
+        <v>726716</v>
       </c>
       <c r="R28" t="n">
-        <v>7354872</v>
+        <v>7354943</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3616,12 +3475,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3649,37 +3508,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121589892</v>
+        <v>121589891</v>
       </c>
       <c r="B29" t="n">
-        <v>78629</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3696,10 +3550,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>726717</v>
+        <v>726725</v>
       </c>
       <c r="R29" t="n">
-        <v>7354967</v>
+        <v>7354940</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3759,48 +3613,56 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126315540</v>
+        <v>121589889</v>
       </c>
       <c r="B30" t="n">
-        <v>79047</v>
+        <v>58057</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>637</v>
+        <v>103031</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ringlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Evernia divaricata</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Sadimoajvve, Lu lm</t>
+          <t>Jokkmokksmyran, Lu lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>726992</v>
+        <v>726331</v>
       </c>
       <c r="R30" t="n">
-        <v>7355076</v>
+        <v>7355214</v>
       </c>
       <c r="S30" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3853,6 +3715,324 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>121589881</v>
+      </c>
+      <c r="B31" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Jokkmokksmyran, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>726603</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7355549</v>
+      </c>
+      <c r="S31" t="n">
+        <v>25</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>121589871</v>
+      </c>
+      <c r="B32" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Jokkmokksmyran, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>726939</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7355544</v>
+      </c>
+      <c r="S32" t="n">
+        <v>25</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>121589895</v>
+      </c>
+      <c r="B33" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Jokkmokksmyran, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>726866</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7354811</v>
+      </c>
+      <c r="S33" t="n">
+        <v>25</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 29675-2024 artfynd.xlsx
+++ b/artfynd/A 29675-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY33"/>
+  <dimension ref="A1:AZ33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121127723</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -880,6 +890,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126315540</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -985,6 +1000,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589883</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1090,6 +1110,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589888</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1195,6 +1220,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589900</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1300,6 +1330,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589876</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1405,6 +1440,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589878</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1510,6 +1550,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589885</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1615,6 +1660,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589899</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1720,6 +1770,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589894</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1825,6 +1880,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589880</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1930,6 +1990,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589898</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2035,6 +2100,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589874</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2140,6 +2210,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589877</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2245,6 +2320,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589882</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2350,6 +2430,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589884</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2455,6 +2540,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589886</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2560,6 +2650,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589887</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2665,6 +2760,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589890</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2770,6 +2870,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589892</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2875,6 +2980,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589896</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2980,6 +3090,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589902</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3085,6 +3200,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589879</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3190,6 +3310,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589897</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3295,6 +3420,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589873</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3400,6 +3530,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589875</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3505,6 +3640,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589893</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3610,6 +3750,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589891</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3715,6 +3860,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589889</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3821,6 +3971,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589881</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3927,6 +4082,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589871</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4033,8 +4193,47 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589895</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>